--- a/Backtest/10-02-20/S&P500stock_10-02-20period252RS90.xlsx
+++ b/Backtest/10-02-20/S&P500stock_10-02-20period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="73">
   <si>
     <t>Stock</t>
   </si>
@@ -127,124 +127,112 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>ACGL</t>
-  </si>
-  <si>
-    <t>CPRT</t>
-  </si>
-  <si>
-    <t>CHTR</t>
-  </si>
-  <si>
-    <t>FICO</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>EPAM</t>
-  </si>
-  <si>
-    <t>MSFT</t>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>FDX</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>CDNS</t>
+  </si>
+  <si>
+    <t>CRWD</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>HUM</t>
+  </si>
+  <si>
+    <t>NFLX</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>DPZ</t>
   </si>
   <si>
     <t>WST</t>
   </si>
   <si>
-    <t>EQIX</t>
-  </si>
-  <si>
-    <t>BX</t>
-  </si>
-  <si>
-    <t>ENPH</t>
-  </si>
-  <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
-    <t>2020-02-11</t>
-  </si>
-  <si>
-    <t>2020-02-19</t>
-  </si>
-  <si>
-    <t>2020-05-01</t>
-  </si>
-  <si>
-    <t>2020-02-20</t>
-  </si>
-  <si>
-    <t>2020-02-13</t>
-  </si>
-  <si>
-    <t>2020-02-12</t>
-  </si>
-  <si>
-    <t>2020-04-23</t>
-  </si>
-  <si>
-    <t>2020-02-18</t>
+    <t>2020-12-01</t>
+  </si>
+  <si>
+    <t>2020-12-17</t>
+  </si>
+  <si>
+    <t>2020-11-18</t>
+  </si>
+  <si>
+    <t>2020-10-19</t>
+  </si>
+  <si>
+    <t>2020-12-02</t>
+  </si>
+  <si>
+    <t>2020-10-27</t>
+  </si>
+  <si>
+    <t>2020-11-03</t>
+  </si>
+  <si>
+    <t>2020-10-20</t>
+  </si>
+  <si>
+    <t>2020-12-10</t>
+  </si>
+  <si>
+    <t>2020-10-08</t>
+  </si>
+  <si>
+    <t>2020-10-22</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Industrials</t>
   </si>
   <si>
     <t>Consumer Cyclical</t>
   </si>
   <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Industrials</t>
+    <t>Healthcare</t>
   </si>
   <si>
     <t>Communication Services</t>
   </si>
   <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
-    <t>Auto Manufacturers</t>
-  </si>
-  <si>
-    <t>Insurance - Diversified</t>
-  </si>
-  <si>
-    <t>Specialty Business Services</t>
-  </si>
-  <si>
-    <t>Telecom Services</t>
-  </si>
-  <si>
     <t>Software - Application</t>
   </si>
   <si>
-    <t>Credit Services</t>
-  </si>
-  <si>
-    <t>Information Technology Services</t>
+    <t>Integrated Freight &amp; Logistics</t>
+  </si>
+  <si>
+    <t>Home Improvement Retail</t>
   </si>
   <si>
     <t>Software - Infrastructure</t>
   </si>
   <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Healthcare Plans</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Restaurants</t>
+  </si>
+  <si>
     <t>Medical Instruments &amp; Supplies</t>
-  </si>
-  <si>
-    <t>REIT - Specialty</t>
-  </si>
-  <si>
-    <t>Asset Management</t>
-  </si>
-  <si>
-    <t>Solar</t>
   </si>
 </sst>
 </file>
@@ -602,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AK12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -723,43 +711,43 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>99.59349593495935</v>
+        <v>94.74747474747474</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="D2">
-        <v>49.87</v>
+        <v>253.45</v>
       </c>
       <c r="E2">
-        <v>7.48</v>
+        <v>2.57</v>
       </c>
       <c r="F2">
-        <v>2.772591835994377</v>
+        <v>0.06269114747521648</v>
       </c>
       <c r="G2">
-        <v>4.71</v>
+        <v>4.04</v>
       </c>
       <c r="H2">
-        <v>2.425634797562552</v>
+        <v>1.416769760118348</v>
       </c>
       <c r="I2">
-        <v>51.98386688232422</v>
+        <v>248.3260009765625</v>
       </c>
       <c r="J2">
-        <v>40.77759990692139</v>
+        <v>247.3270011901855</v>
       </c>
       <c r="K2">
-        <v>31.89649333953857</v>
+        <v>227.3676013183594</v>
       </c>
       <c r="L2">
-        <v>20.30842670440674</v>
+        <v>185.7058502960205</v>
       </c>
       <c r="M2">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>1.63</v>
+        <v>1.09</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -771,10 +759,10 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2">
-        <v>8.333333333333332</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -783,49 +771,49 @@
         <v>1</v>
       </c>
       <c r="W2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2">
-        <v>11.8</v>
+        <v>115.29</v>
       </c>
       <c r="Y2">
-        <v>64.59999999999999</v>
+        <v>284.5</v>
       </c>
       <c r="Z2">
-        <v>74.20999999999999</v>
+        <v>179.65</v>
       </c>
       <c r="AA2">
-        <v>114.77</v>
+        <v>-1401.66</v>
       </c>
       <c r="AB2">
-        <v>49.99</v>
+        <v>125.89</v>
       </c>
       <c r="AC2">
-        <v>117.31</v>
+        <v>2516.67</v>
       </c>
       <c r="AD2">
-        <v>1.77</v>
+        <v>6.83</v>
       </c>
       <c r="AE2">
-        <v>-11.26</v>
+        <v>2536.36</v>
       </c>
       <c r="AF2">
-        <v>134.61</v>
+        <v>130.56</v>
       </c>
       <c r="AG2">
-        <v>43.65</v>
+        <v>-200</v>
       </c>
       <c r="AH2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AK2">
-        <v>62.57492377282434</v>
+        <v>91.11111111111111</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -833,61 +821,61 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>90.04065040650406</v>
+        <v>95.75757575757575</v>
       </c>
       <c r="C3">
-        <v>308</v>
+        <v>192</v>
       </c>
       <c r="D3">
-        <v>46.15</v>
+        <v>254.08</v>
       </c>
       <c r="E3">
-        <v>0.83</v>
+        <v>2.21</v>
       </c>
       <c r="F3">
-        <v>-0.62398213564135</v>
+        <v>-0.5906165998980898</v>
       </c>
       <c r="G3">
-        <v>0.92</v>
+        <v>2.19</v>
       </c>
       <c r="H3">
-        <v>-0.566441974695242</v>
+        <v>-0.3908330372740274</v>
       </c>
       <c r="I3">
-        <v>45.51200027465821</v>
+        <v>252.7420013427734</v>
       </c>
       <c r="J3">
-        <v>44.75349998474121</v>
+        <v>239.6400001525879</v>
       </c>
       <c r="K3">
-        <v>43.2076000213623</v>
+        <v>213.0372006225586</v>
       </c>
       <c r="L3">
-        <v>39.64280000686645</v>
+        <v>156.1088000488281</v>
       </c>
       <c r="M3">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N3">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
@@ -896,46 +884,46 @@
         <v>1</v>
       </c>
       <c r="X3">
-        <v>29.95</v>
+        <v>88.69</v>
       </c>
       <c r="Y3">
-        <v>46.66</v>
+        <v>259.95</v>
       </c>
       <c r="Z3">
-        <v>17.35</v>
+        <v>57.82</v>
       </c>
       <c r="AA3">
-        <v>11.47</v>
+        <v>3.4</v>
       </c>
       <c r="AB3">
-        <v>53.98</v>
+        <v>73.72</v>
       </c>
       <c r="AC3">
-        <v>216.67</v>
+        <v>120.93</v>
       </c>
       <c r="AD3">
-        <v>3.55</v>
+        <v>6.4</v>
       </c>
       <c r="AE3">
-        <v>-16.67</v>
+        <v>465.38</v>
       </c>
       <c r="AF3">
-        <v>4.59</v>
+        <v>-207.44</v>
       </c>
       <c r="AG3">
-        <v>263.33</v>
+        <v>-43.72</v>
       </c>
       <c r="AH3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AI3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AK3">
-        <v>56.50544981324126</v>
+        <v>75.16589343980975</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -943,49 +931,49 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>98.98373983739837</v>
+        <v>90.50505050505051</v>
       </c>
       <c r="C4">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="D4">
-        <v>25.65</v>
+        <v>167.17</v>
       </c>
       <c r="E4">
-        <v>0.8100000000000001</v>
+        <v>2.23</v>
       </c>
       <c r="F4">
-        <v>-0.6341973957064199</v>
+        <v>-0.5543217250440171</v>
       </c>
       <c r="G4">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="H4">
-        <v>-0.4717060346765256</v>
+        <v>-0.9477701153895158</v>
       </c>
       <c r="I4">
-        <v>25.55700035095215</v>
+        <v>163.4859985351563</v>
       </c>
       <c r="J4">
-        <v>24.91525001525879</v>
+        <v>161.5960014343262</v>
       </c>
       <c r="K4">
-        <v>23.50820014953613</v>
+        <v>158.5792007446289</v>
       </c>
       <c r="L4">
-        <v>20.26920009613037</v>
+        <v>125.9469002151489</v>
       </c>
       <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
         <v>1.03</v>
       </c>
-      <c r="N4">
-        <v>1.09</v>
-      </c>
       <c r="P4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -994,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>7.777777777777777</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="U4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="b">
         <v>1</v>
@@ -1006,46 +994,46 @@
         <v>1</v>
       </c>
       <c r="X4">
-        <v>12.76</v>
+        <v>60</v>
       </c>
       <c r="Y4">
-        <v>26.02</v>
+        <v>171.72</v>
       </c>
       <c r="Z4">
-        <v>19.72</v>
+        <v>112.13</v>
       </c>
       <c r="AA4">
-        <v>262.15</v>
+        <v>10.67</v>
       </c>
       <c r="AB4">
-        <v>19.84</v>
+        <v>63.91</v>
       </c>
       <c r="AC4">
-        <v>64.91</v>
+        <v>175</v>
       </c>
       <c r="AD4">
-        <v>11.32</v>
+        <v>64.92</v>
       </c>
       <c r="AE4">
-        <v>42.42</v>
+        <v>112.5</v>
       </c>
       <c r="AF4">
-        <v>-22.35</v>
+        <v>158.82</v>
       </c>
       <c r="AG4">
-        <v>49.12</v>
+        <v>-50</v>
       </c>
       <c r="AH4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AI4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AJ4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AK4">
-        <v>48.9690038485065</v>
+        <v>67.214030948258</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1053,59 +1041,59 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>90.44715447154471</v>
+        <v>93.73737373737374</v>
       </c>
       <c r="C5">
-        <v>336</v>
+        <v>277</v>
       </c>
       <c r="D5">
-        <v>525.21</v>
+        <v>108.63</v>
       </c>
       <c r="E5">
-        <v>1.63</v>
+        <v>2.85</v>
       </c>
       <c r="F5">
-        <v>-0.2153717330385559</v>
+        <v>0.570819395432233</v>
       </c>
       <c r="G5">
-        <v>1.16</v>
+        <v>2.1</v>
       </c>
       <c r="H5">
-        <v>-0.3769700946578092</v>
+        <v>-0.4787704706606834</v>
       </c>
       <c r="I5">
-        <v>527.55</v>
+        <v>106.0019989013672</v>
       </c>
       <c r="J5">
-        <v>511.2980026245117</v>
+        <v>103.5575004577637</v>
       </c>
       <c r="K5">
-        <v>491.2803997802735</v>
+        <v>106.8246002197266</v>
       </c>
       <c r="L5">
-        <v>430.4139500427246</v>
+        <v>85.57354991912842</v>
       </c>
       <c r="M5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N5">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="P5">
+        <v>7</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
         <v>5</v>
       </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>2.777777777777778</v>
-      </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
@@ -1116,46 +1104,46 @@
         <v>1</v>
       </c>
       <c r="X5">
-        <v>335.22</v>
+        <v>51.39</v>
       </c>
       <c r="Y5">
-        <v>537.54</v>
+        <v>117.59</v>
       </c>
       <c r="Z5">
-        <v>108.55</v>
+        <v>26.78</v>
       </c>
       <c r="AA5">
-        <v>-21.05</v>
+        <v>80.73</v>
       </c>
       <c r="AB5">
-        <v>18.38</v>
+        <v>93.75</v>
       </c>
       <c r="AC5">
-        <v>191.15</v>
+        <v>29.73</v>
       </c>
       <c r="AD5">
-        <v>2.12</v>
+        <v>5.82</v>
       </c>
       <c r="AE5">
-        <v>85.88</v>
+        <v>6.67</v>
       </c>
       <c r="AF5">
-        <v>25.53</v>
+        <v>-81.40000000000001</v>
       </c>
       <c r="AG5">
-        <v>24.78</v>
+        <v>554.05</v>
       </c>
       <c r="AH5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AI5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AJ5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="AK5">
-        <v>47.5837064472963</v>
+        <v>62.90130207083159</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1163,61 +1151,61 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>97.96747967479675</v>
+        <v>98.38383838383838</v>
       </c>
       <c r="C6">
-        <v>481</v>
+        <v>134</v>
       </c>
       <c r="D6">
-        <v>417.6</v>
+        <v>142.87</v>
       </c>
       <c r="E6">
-        <v>1.39</v>
+        <v>3.22</v>
       </c>
       <c r="F6">
-        <v>-0.3379548538193942</v>
+        <v>1.242274580232576</v>
       </c>
       <c r="G6">
-        <v>1.18</v>
+        <v>3.66</v>
       </c>
       <c r="H6">
-        <v>-0.3611807713213565</v>
+        <v>1.045478374708022</v>
       </c>
       <c r="I6">
-        <v>415.9079956054687</v>
+        <v>138.0720001220703</v>
       </c>
       <c r="J6">
-        <v>409.4554992675781</v>
+        <v>132.9329990386963</v>
       </c>
       <c r="K6">
-        <v>385.9734002685547</v>
+        <v>119.8956997680664</v>
       </c>
       <c r="L6">
-        <v>336.4537498474121</v>
+        <v>83.23207485198975</v>
       </c>
       <c r="M6">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
         <v>2</v>
       </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
       <c r="T6">
-        <v>1.111111111111111</v>
+        <v>5</v>
       </c>
       <c r="U6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="b">
         <v>1</v>
@@ -1226,46 +1214,46 @@
         <v>1</v>
       </c>
       <c r="X6">
-        <v>231.14</v>
+        <v>31.95</v>
       </c>
       <c r="Y6">
-        <v>426.98</v>
+        <v>153.1</v>
       </c>
       <c r="Z6">
-        <v>11.3</v>
+        <v>24.53</v>
       </c>
       <c r="AA6">
-        <v>12.65</v>
+        <v>0.15</v>
       </c>
       <c r="AB6">
-        <v>25.26</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="AC6">
-        <v>64.34999999999999</v>
+        <v>17.65</v>
       </c>
       <c r="AD6">
-        <v>22.79</v>
+        <v>-3.77</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>-55.56</v>
       </c>
       <c r="AF6">
-        <v>-14.48</v>
+        <v>-156.25</v>
       </c>
       <c r="AG6">
-        <v>92.17</v>
+        <v>194.12</v>
       </c>
       <c r="AH6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AI6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="AJ6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AK6">
-        <v>43.50254014272317</v>
+        <v>59.51877177509589</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1273,49 +1261,49 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>90.65040650406505</v>
+        <v>99.19191919191918</v>
       </c>
       <c r="C7">
-        <v>164</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>327</v>
+        <v>84.86</v>
       </c>
       <c r="E7">
-        <v>1.38</v>
+        <v>3.35</v>
       </c>
       <c r="F7">
-        <v>-0.3430624838519291</v>
+        <v>1.478191266784048</v>
       </c>
       <c r="G7">
+        <v>4.29</v>
+      </c>
+      <c r="H7">
+        <v>1.661040408414615</v>
+      </c>
+      <c r="I7">
+        <v>81.23199920654297</v>
+      </c>
+      <c r="J7">
+        <v>78.88950080871582</v>
+      </c>
+      <c r="K7">
+        <v>80.18559997558594</v>
+      </c>
+      <c r="L7">
+        <v>58.06005001068115</v>
+      </c>
+      <c r="M7">
+        <v>1.03</v>
+      </c>
+      <c r="N7">
         <v>1.01</v>
       </c>
-      <c r="H7">
-        <v>-0.4953900196812047</v>
-      </c>
-      <c r="I7">
-        <v>327.6519958496094</v>
-      </c>
-      <c r="J7">
-        <v>321.256999206543</v>
-      </c>
-      <c r="K7">
-        <v>305.7875994873047</v>
-      </c>
-      <c r="L7">
-        <v>278.1210501861572</v>
-      </c>
-      <c r="M7">
-        <v>1.02</v>
-      </c>
-      <c r="N7">
-        <v>1.07</v>
-      </c>
       <c r="P7">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -1324,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>6.11111111111111</v>
+        <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
@@ -1336,46 +1324,46 @@
         <v>1</v>
       </c>
       <c r="X7">
-        <v>212</v>
+        <v>27.43</v>
       </c>
       <c r="Y7">
-        <v>335</v>
+        <v>94.28</v>
       </c>
       <c r="Z7">
-        <v>305.16</v>
+        <v>64.55</v>
       </c>
       <c r="AA7">
-        <v>9.98</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="AB7">
-        <v>7.26</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="AC7">
-        <v>14.92</v>
+        <v>18.18</v>
       </c>
       <c r="AD7">
-        <v>35.49</v>
+        <v>4.75</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>-7.14</v>
       </c>
       <c r="AF7">
-        <v>3.48</v>
+        <v>-12.5</v>
       </c>
       <c r="AG7">
-        <v>11.05</v>
+        <v>45.45</v>
       </c>
       <c r="AH7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AI7" t="s">
         <v>59</v>
       </c>
       <c r="AJ7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AK7">
-        <v>29.4510403039489</v>
+        <v>55.69591236965997</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1383,43 +1371,43 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>93.69918699186992</v>
+        <v>91.71717171717172</v>
       </c>
       <c r="C8">
-        <v>485</v>
+        <v>418</v>
       </c>
       <c r="D8">
-        <v>233.02</v>
+        <v>415.36</v>
       </c>
       <c r="E8">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="F8">
-        <v>-0.2664480333639052</v>
+        <v>-1.207629472417323</v>
       </c>
       <c r="G8">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="H8">
-        <v>-0.1559195679474708</v>
+        <v>-0.9575409413213666</v>
       </c>
       <c r="I8">
-        <v>234.5500030517578</v>
+        <v>406.3200012207031</v>
       </c>
       <c r="J8">
-        <v>231.1130004882812</v>
+        <v>401.0450012207031</v>
       </c>
       <c r="K8">
-        <v>219.4566003417969</v>
+        <v>405.3006011962891</v>
       </c>
       <c r="L8">
-        <v>192.4931499481201</v>
+        <v>371.5860995483399</v>
       </c>
       <c r="M8">
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1437,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
@@ -1446,46 +1434,46 @@
         <v>1</v>
       </c>
       <c r="X8">
-        <v>143.19</v>
+        <v>208.25</v>
       </c>
       <c r="Y8">
-        <v>242.09</v>
+        <v>431.12</v>
       </c>
       <c r="Z8">
-        <v>10.55</v>
+        <v>51.58</v>
       </c>
       <c r="AA8">
-        <v>25.58</v>
+        <v>4.62</v>
       </c>
       <c r="AB8">
-        <v>16.2</v>
+        <v>12.26</v>
       </c>
       <c r="AC8">
-        <v>9.91</v>
+        <v>168.02</v>
       </c>
       <c r="AD8">
-        <v>4.49</v>
+        <v>12.68</v>
       </c>
       <c r="AE8">
-        <v>14.02</v>
+        <v>286.31</v>
       </c>
       <c r="AF8">
-        <v>-4.46</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="AG8">
-        <v>0.9</v>
+        <v>-24.42</v>
       </c>
       <c r="AH8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AI8" t="s">
         <v>62</v>
       </c>
       <c r="AJ8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AK8">
-        <v>28.37783013808662</v>
+        <v>46.54535299088607</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1493,49 +1481,49 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>96.54471544715447</v>
+        <v>96.96969696969697</v>
       </c>
       <c r="C9">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="D9">
-        <v>183.89</v>
+        <v>527.51</v>
       </c>
       <c r="E9">
-        <v>1.45</v>
+        <v>2.82</v>
       </c>
       <c r="F9">
-        <v>-0.3073090736241846</v>
+        <v>0.5163770831511237</v>
       </c>
       <c r="G9">
-        <v>1.03</v>
+        <v>3.03</v>
       </c>
       <c r="H9">
-        <v>-0.4796006963447519</v>
+        <v>0.4299163410014293</v>
       </c>
       <c r="I9">
-        <v>180.3839996337891</v>
+        <v>498.9100036621094</v>
       </c>
       <c r="J9">
-        <v>169.3934989929199</v>
+        <v>491.2369995117188</v>
       </c>
       <c r="K9">
-        <v>160.7879998779297</v>
+        <v>495.901000366211</v>
       </c>
       <c r="L9">
-        <v>142.4380500030518</v>
+        <v>422.0429002380371</v>
       </c>
       <c r="M9">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N9">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="P9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -1544,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>2.777777777777778</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
@@ -1556,46 +1544,46 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>104.26</v>
+        <v>257.01</v>
       </c>
       <c r="Y9">
-        <v>185.63</v>
+        <v>575.37</v>
       </c>
       <c r="Z9">
-        <v>1212.87</v>
+        <v>206.56</v>
       </c>
       <c r="AA9">
-        <v>11.99</v>
+        <v>445.46</v>
       </c>
       <c r="AB9">
-        <v>5.26</v>
+        <v>46.39</v>
       </c>
       <c r="AC9">
-        <v>33.04</v>
+        <v>7.24</v>
       </c>
       <c r="AD9">
-        <v>10.58</v>
+        <v>7.72</v>
       </c>
       <c r="AE9">
-        <v>9.289999999999999</v>
+        <v>1.24</v>
       </c>
       <c r="AF9">
-        <v>-18.6</v>
+        <v>21.05</v>
       </c>
       <c r="AG9">
-        <v>49.57</v>
+        <v>-12.5</v>
       </c>
       <c r="AH9" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AI9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AJ9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AK9">
-        <v>26.21333205586271</v>
+        <v>43.25508230034485</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1603,43 +1591,43 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>91.46341463414635</v>
+        <v>96.56565656565657</v>
       </c>
       <c r="C10">
-        <v>473</v>
+        <v>203</v>
       </c>
       <c r="D10">
-        <v>159.09</v>
+        <v>499.51</v>
       </c>
       <c r="E10">
-        <v>0.8100000000000001</v>
+        <v>2.85</v>
       </c>
       <c r="F10">
-        <v>-0.6341973957064199</v>
+        <v>0.570819395432233</v>
       </c>
       <c r="G10">
-        <v>0.84</v>
+        <v>2.62</v>
       </c>
       <c r="H10">
-        <v>-0.629599268041053</v>
+        <v>0.02931247779555184</v>
       </c>
       <c r="I10">
-        <v>159.2540008544922</v>
+        <v>489.5119995117187</v>
       </c>
       <c r="J10">
-        <v>157.321501159668</v>
+        <v>481.9205017089844</v>
       </c>
       <c r="K10">
-        <v>152.3928005981445</v>
+        <v>471.7764013671875</v>
       </c>
       <c r="L10">
-        <v>138.4746000671387</v>
+        <v>390.5121008300781</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N10">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -1657,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="b">
         <v>1</v>
@@ -1666,46 +1654,46 @@
         <v>1</v>
       </c>
       <c r="X10">
-        <v>98.59999999999999</v>
+        <v>255.13</v>
       </c>
       <c r="Y10">
-        <v>161.21</v>
+        <v>536.88</v>
       </c>
       <c r="Z10">
-        <v>10.71</v>
+        <v>248.99</v>
       </c>
       <c r="AA10">
-        <v>13.84</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="AB10">
-        <v>11.47</v>
+        <v>7.37</v>
       </c>
       <c r="AC10">
-        <v>8.57</v>
+        <v>13.07</v>
       </c>
       <c r="AD10">
-        <v>3.78</v>
+        <v>8.15</v>
       </c>
       <c r="AE10">
-        <v>-15.56</v>
+        <v>-12.72</v>
       </c>
       <c r="AF10">
-        <v>20</v>
+        <v>15.15</v>
       </c>
       <c r="AG10">
-        <v>7.14</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AI10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AJ10" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="AK10">
-        <v>24.1289178545712</v>
+        <v>25.85292661528925</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1713,43 +1701,43 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>91.66666666666666</v>
+        <v>94.94949494949495</v>
       </c>
       <c r="C11">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="D11">
-        <v>606</v>
+        <v>426.99</v>
       </c>
       <c r="E11">
-        <v>1.07</v>
+        <v>1.56</v>
       </c>
       <c r="F11">
-        <v>-0.5013990148605117</v>
+        <v>-1.770200032655449</v>
       </c>
       <c r="G11">
-        <v>1.09</v>
+        <v>1.41</v>
       </c>
       <c r="H11">
-        <v>-0.4322327263353937</v>
+        <v>-1.15295745995838</v>
       </c>
       <c r="I11">
-        <v>604.48798828125</v>
+        <v>423.0699951171875</v>
       </c>
       <c r="J11">
-        <v>596.4345001220703</v>
+        <v>401.9469985961914</v>
       </c>
       <c r="K11">
-        <v>579.8201977539062</v>
+        <v>400.8463989257813</v>
       </c>
       <c r="L11">
-        <v>541.1843997192383</v>
+        <v>355.7770503234863</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N11">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -1767,7 +1755,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
@@ -1776,46 +1764,46 @@
         <v>1</v>
       </c>
       <c r="X11">
-        <v>385.91</v>
+        <v>227.5</v>
       </c>
       <c r="Y11">
-        <v>609.97</v>
+        <v>430.91</v>
       </c>
       <c r="Z11">
-        <v>49.36</v>
+        <v>14.68</v>
       </c>
       <c r="AA11">
-        <v>-7.24</v>
+        <v>15.11</v>
       </c>
       <c r="AB11">
-        <v>9.59</v>
+        <v>1.06</v>
       </c>
       <c r="AC11">
-        <v>2.9</v>
+        <v>44.08</v>
       </c>
       <c r="AD11">
-        <v>1.38</v>
+        <v>-3.61</v>
       </c>
       <c r="AE11">
-        <v>-16.47</v>
+        <v>-3.18</v>
       </c>
       <c r="AF11">
-        <v>18.06</v>
+        <v>-1.88</v>
       </c>
       <c r="AG11">
-        <v>4.35</v>
+        <v>51.66</v>
       </c>
       <c r="AH11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AI11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AJ11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="AK11">
-        <v>17.75670303851252</v>
+        <v>16.25706388182987</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1823,49 +1811,49 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>98.17073170731707</v>
+        <v>97.57575757575758</v>
       </c>
       <c r="C12">
-        <v>172</v>
+        <v>463</v>
       </c>
       <c r="D12">
-        <v>62.76</v>
+        <v>275.79</v>
       </c>
       <c r="E12">
-        <v>1.86</v>
+        <v>2.36</v>
       </c>
       <c r="F12">
-        <v>-0.09789624229025252</v>
+        <v>-0.3184050384925456</v>
       </c>
       <c r="G12">
-        <v>1.34</v>
+        <v>1.92</v>
       </c>
       <c r="H12">
-        <v>-0.2348661846297344</v>
+        <v>-0.6546453374339958</v>
       </c>
       <c r="I12">
-        <v>62.8979995727539</v>
+        <v>273.2480041503906</v>
       </c>
       <c r="J12">
-        <v>61.2754997253418</v>
+        <v>273.1110015869141</v>
       </c>
       <c r="K12">
-        <v>57.4715998840332</v>
+        <v>272.8336004638672</v>
       </c>
       <c r="L12">
-        <v>49.52205003738403</v>
+        <v>203.1841497039795</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="N12">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1874,7 +1862,7 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>2.777777777777778</v>
+        <v>0</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
@@ -1886,156 +1874,46 @@
         <v>1</v>
       </c>
       <c r="X12">
-        <v>32.39</v>
+        <v>124.53</v>
       </c>
       <c r="Y12">
-        <v>64.39</v>
+        <v>288.65</v>
       </c>
       <c r="Z12">
-        <v>37.82</v>
+        <v>17.15</v>
       </c>
       <c r="AA12">
-        <v>4.65</v>
+        <v>25.27</v>
       </c>
       <c r="AB12">
-        <v>1.68</v>
+        <v>0.26</v>
       </c>
       <c r="AC12">
-        <v>1.41</v>
+        <v>63.16</v>
       </c>
       <c r="AD12">
-        <v>6.52</v>
+        <v>5.68</v>
       </c>
       <c r="AE12">
-        <v>-37.39</v>
+        <v>22.77</v>
       </c>
       <c r="AF12">
-        <v>155.56</v>
+        <v>17.44</v>
       </c>
       <c r="AG12">
-        <v>-36.62</v>
+        <v>13.16</v>
       </c>
       <c r="AH12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AI12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AJ12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="AK12">
-        <v>3.333333333333334</v>
-      </c>
-    </row>
-    <row r="13" spans="1:37">
-      <c r="A13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13">
-        <v>100</v>
-      </c>
-      <c r="C13">
-        <v>88</v>
-      </c>
-      <c r="D13">
-        <v>38.05</v>
-      </c>
-      <c r="E13">
-        <v>4.38</v>
-      </c>
-      <c r="F13">
-        <v>1.189226525908549</v>
-      </c>
-      <c r="G13">
-        <v>3.89</v>
-      </c>
-      <c r="H13">
-        <v>1.77827254076799</v>
-      </c>
-      <c r="I13">
-        <v>36.63399963378906</v>
-      </c>
-      <c r="J13">
-        <v>32.73650035858154</v>
-      </c>
-      <c r="K13">
-        <v>28.57660026550293</v>
-      </c>
-      <c r="L13">
-        <v>23.17140009880066</v>
-      </c>
-      <c r="M13">
-        <v>1.12</v>
-      </c>
-      <c r="N13">
-        <v>1.28</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>1</v>
-      </c>
-      <c r="T13">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="U13" t="b">
-        <v>0</v>
-      </c>
-      <c r="V13" t="b">
-        <v>1</v>
-      </c>
-      <c r="W13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>7.01</v>
-      </c>
-      <c r="Y13">
-        <v>38.88</v>
-      </c>
-      <c r="Z13">
-        <v>2.97</v>
-      </c>
-      <c r="AA13">
-        <v>-112.43</v>
-      </c>
-      <c r="AB13">
-        <v>371.43</v>
-      </c>
-      <c r="AC13">
-        <v>2400</v>
-      </c>
-      <c r="AD13">
-        <v>20.42</v>
-      </c>
-      <c r="AE13">
-        <v>177.78</v>
-      </c>
-      <c r="AF13">
-        <v>200</v>
-      </c>
-      <c r="AG13">
-        <v>200</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>62</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>76</v>
-      </c>
-      <c r="AK13">
-        <v>92</v>
+        <v>12.55368260201255</v>
       </c>
     </row>
   </sheetData>
